--- a/data.mn/public/datasets/mongolbank-external-debt.xlsx
+++ b/data.mn/public/datasets/mongolbank-external-debt.xlsx
@@ -8,7 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="English" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Mongolian" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Монгол" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/data.mn/public/datasets/mongolbank-external-debt.xlsx
+++ b/data.mn/public/datasets/mongolbank-external-debt.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B106"/>
+  <dimension ref="A1:B107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1481,6 +1481,16 @@
       </c>
       <c r="B106" t="n">
         <v>40217.55</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B107" t="n">
+        <v>39144.28</v>
       </c>
     </row>
   </sheetData>
@@ -1494,7 +1504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B106"/>
+  <dimension ref="A1:B107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2563,6 +2573,16 @@
         <v>40217.55</v>
       </c>
     </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B107" t="n">
+        <v>39144.28</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
